--- a/Estadística 1/Taller 1 estadistica.xlsx
+++ b/Estadística 1/Taller 1 estadistica.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5952D5DC84431EC9/Documentos/Unaula clases/Estadística 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{9863C9E7-05CD-4DF0-A4D2-5B92691768CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B61622-114C-4EFA-9558-39E543239DA9}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{9863C9E7-05CD-4DF0-A4D2-5B92691768CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC1933B4-B8B3-40EA-A556-DB3675F98EA5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C4F1C481-FEE4-4FD3-954B-B4F627803B9A}"/>
   </bookViews>
@@ -524,6 +524,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -536,14 +544,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2112,10 +2112,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>17.2</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>12</c:v>
@@ -15619,15 +15619,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>248047</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>143493</xdr:rowOff>
+      <xdr:colOff>180812</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>68788</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>29766</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>99219</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>724531</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>24513</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -15642,8 +15642,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7123906" y="2217165"/>
-          <a:ext cx="2837657" cy="898304"/>
+          <a:off x="7195694" y="2309964"/>
+          <a:ext cx="2829719" cy="889549"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16370,10 +16370,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="7"/>
       <c r="F9" s="10"/>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="10">
         <v>0</v>
       </c>
@@ -16916,10 +16916,10 @@
         <v>7</v>
       </c>
       <c r="F8" s="10"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="10">
         <v>0</v>
       </c>
@@ -17397,7 +17397,7 @@
       <c r="C2" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="27">
         <v>9</v>
       </c>
       <c r="E2" s="15">
@@ -17410,7 +17410,7 @@
         <f>+F2/F7</f>
         <v>0.2</v>
       </c>
-      <c r="H2" s="30">
+      <c r="H2" s="26">
         <f>+F2</f>
         <v>4</v>
       </c>
@@ -17423,14 +17423,14 @@
         <v>10.1</v>
       </c>
       <c r="K2" s="16">
-        <f>+K3+G2</f>
-        <v>17.2</v>
+        <f>+K3+F2</f>
+        <v>20</v>
       </c>
       <c r="L2" s="16">
         <f>+F2*J2</f>
         <v>40.4</v>
       </c>
-      <c r="M2" s="29"/>
+      <c r="M2" s="25"/>
       <c r="N2">
         <v>77.44</v>
       </c>
@@ -17468,8 +17468,8 @@
         <v>12.3</v>
       </c>
       <c r="K3" s="16">
-        <f>+K4+F4</f>
-        <v>17</v>
+        <f>+K4+F3</f>
+        <v>16</v>
       </c>
       <c r="L3" s="16">
         <f>+F3*J3</f>
@@ -17619,10 +17619,10 @@
       <c r="N6">
         <v>96.8</v>
       </c>
-      <c r="P6" s="32" t="s">
+      <c r="P6" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="Q6" s="34" t="s">
+      <c r="Q6" s="30" t="s">
         <v>50</v>
       </c>
     </row>
@@ -17631,10 +17631,10 @@
         <v>33</v>
       </c>
       <c r="C7" s="15"/>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="28"/>
+      <c r="E7" s="36"/>
       <c r="F7" s="17">
         <f>SUM(F2:F6)</f>
         <v>20</v>
@@ -17659,11 +17659,11 @@
         <f>+N7/20</f>
         <v>10.163999999999998</v>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="29">
         <f>SQRT(O7)</f>
         <v>3.1881028841616761</v>
       </c>
-      <c r="Q7" s="35">
+      <c r="Q7" s="31">
         <f>+P7/14.5</f>
         <v>0.21986916442494317</v>
       </c>
@@ -17672,7 +17672,7 @@
       <c r="A8" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="Q8" s="36">
+      <c r="Q8" s="32">
         <f>+Q7*100</f>
         <v>21.986916442494316</v>
       </c>
